--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrBrowDepoInfo002.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrBrowDepoInfo002.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IdeaProjects\GUANGZHOU\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="12915" windowHeight="5985"/>
   </bookViews>
@@ -17,11 +12,12 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>组合代码</t>
   </si>
@@ -74,10 +70,6 @@
   <si>
     <t>资产三级分类</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>当前处理人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -512,9 +504,6 @@
       <c r="P1" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrBrowDepoInfo002.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrBrowDepoInfo002.xlsx
@@ -3,6 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\git\dcretams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="12915" windowHeight="5985"/>
   </bookViews>
@@ -12,12 +17,11 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>组合代码</t>
   </si>
@@ -70,6 +74,10 @@
   <si>
     <t>资产三级分类</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>投资经理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -443,16 +451,17 @@
   <dimension ref="A1:Q1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="3" width="15.5" customWidth="1"/>
-    <col min="4" max="4" width="14.75" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="15.25" customWidth="1"/>
-    <col min="7" max="7" width="14.375" customWidth="1"/>
-    <col min="8" max="8" width="13.625" customWidth="1"/>
-    <col min="9" max="9" width="11.5" customWidth="1"/>
-    <col min="10" max="10" width="11.375" customWidth="1"/>
-    <col min="11" max="12" width="11.25" customWidth="1"/>
-    <col min="13" max="13" width="12.75" customWidth="1"/>
+    <col min="2" max="2" width="11.25" customWidth="1"/>
+    <col min="3" max="4" width="15.5" customWidth="1"/>
+    <col min="5" max="5" width="14.75" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="15.25" customWidth="1"/>
+    <col min="8" max="8" width="14.375" customWidth="1"/>
+    <col min="9" max="9" width="13.625" customWidth="1"/>
+    <col min="10" max="10" width="11.5" customWidth="1"/>
+    <col min="11" max="11" width="11.375" customWidth="1"/>
+    <col min="12" max="13" width="11.25" customWidth="1"/>
+    <col min="14" max="14" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.15">
@@ -460,48 +469,51 @@
         <v>13</v>
       </c>
       <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>6</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>7</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>8</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>9</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>10</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>11</v>
       </c>
     </row>
